--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>31.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>165.</t>
+          <t>175.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2380.</t>
+          <t>2394.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5198.</t>
+          <t>5322.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>669.</t>
+          <t>679.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>752.</t>
+          <t>756.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>142.</t>
+          <t>164.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2237.</t>
+          <t>2354.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>372.</t>
+          <t>390.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31.</t>
+          <t>64.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>175.</t>
+          <t>261.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2394.</t>
+          <t>2215.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5322.</t>
+          <t>137.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,53 +718,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>679.</t>
+          <t>5474.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08-Jun-2026 05:00 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18-Jun-2026 04:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5,97,82,330</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>59782330</v>
+        <v>10000000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -784,17 +784,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>756.</t>
+          <t>714.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08-Jun-2026 11:00 AM</t>
+          <t>08-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18-Jun-2026 05:00 PM</t>
+          <t>18-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -804,25 +804,25 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3,87,50,583</t>
+          <t>5,97,82,330</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>38750583</v>
+        <v>59782330</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>164.</t>
+          <t>773.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>08-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>18-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>19-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>PWD</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>3,87,50,583</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31803649</v>
+        <v>38750583</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,45 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2354.</t>
+          <t>244.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30-May-2026 01:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19-Jun-2026 03:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2,70,53,943</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>27053943</v>
+        <v>31803649</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,43 +958,101 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>390.</t>
+          <t>2722.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>30-May-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>19-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2,70,53,943</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>27053943</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Punjab eProcurement</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>608.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>1,67,51,919</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>16751919</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64.</t>
+          <t>95.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>261.</t>
+          <t>378.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2215.</t>
+          <t>196.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>15861542</v>
+        <v>11000000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,53 +660,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>137.</t>
+          <t>810.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>08-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>18-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>19-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>5,97,82,330</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11000000</v>
+        <v>59782330</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,53 +718,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5474.</t>
+          <t>853.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>08-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>18-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>19-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>PWD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>3,87,50,583</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10000000</v>
+        <v>38750583</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,45 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>714.</t>
+          <t>661.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08-Jun-2026 05:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18-Jun-2026 04:00 PM</t>
+          <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
+          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5,97,82,330</t>
+          <t>3,44,40,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>59782330</v>
+        <v>34440000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>773.</t>
+          <t>195.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08-Jun-2026 11:00 AM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3,87,50,583</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>38750583</v>
+        <v>31984321</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>244.</t>
+          <t>364.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2722.</t>
+          <t>2637.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>608.</t>
+          <t>655.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>95.</t>
+          <t>129.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>378.</t>
+          <t>494.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>196.</t>
+          <t>2394.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11000000</v>
+        <v>15861542</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,53 +660,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>810.</t>
+          <t>328.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08-Jun-2026 05:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18-Jun-2026 04:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5,97,82,330</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>59782330</v>
+        <v>11000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>853.</t>
+          <t>905.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>661.</t>
+          <t>1332.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>195.</t>
+          <t>514.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>364.</t>
+          <t>548.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2637.</t>
+          <t>2671.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>655.</t>
+          <t>781.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>129.</t>
+          <t>631.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>12-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>23-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>HP SIDC Limited</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>2,79,52,391</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>29140100</v>
+        <v>27952391</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -552,45 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>494.</t>
+          <t>2096.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-Jun-2026 11:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HP SIDC Limited</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2,79,52,391</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>27952391</v>
+        <v>15861542</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2394.</t>
+          <t>698.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>15861542</v>
+        <v>11000000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>328.</t>
+          <t>5771.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -726,45 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>905.</t>
+          <t>2555.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08-Jun-2026 11:00 AM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18-Jun-2026 05:00 PM</t>
+          <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
+          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3,87,50,583</t>
+          <t>3,44,40,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>38750583</v>
+        <v>34440000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1332.</t>
+          <t>926.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -794,35 +794,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19-Jun-2026 06:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3,44,40,000</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>34440000</v>
+        <v>31984321</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>514.</t>
+          <t>933.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31984321</v>
+        <v>31803649</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,45 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>548.</t>
+          <t>3055.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>30-May-2026 01:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>19-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>20-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>2,70,53,943</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>31803649</v>
+        <v>27053943</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,101 +958,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2671.</t>
+          <t>1091.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30-May-2026 01:00 PM</t>
+          <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19-Jun-2026 03:00 PM</t>
+          <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2,70,53,943</t>
+          <t>1,67,51,919</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>27053943</v>
+        <v>16751919</v>
       </c>
       <c r="L10" t="inlineStr">
-        <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Punjab eProcurement</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>32</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>781.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1,67,51,919</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>16751919</v>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>631.</t>
+          <t>244.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-Jun-2026 11:00 AM</t>
+          <t>12-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>30-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
+          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HP SIDC Limited</t>
+          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2,79,52,391</t>
+          <t>2,91,40,100</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>27952391</v>
+        <v>29140100</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -552,45 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2096.</t>
+          <t>636.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>12-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>23-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>HP SIDC Limited</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>2,79,52,391</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>15861542</v>
+        <v>27952391</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>698.</t>
+          <t>2100.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11000000</v>
+        <v>15861542</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5771.</t>
+          <t>714.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -722,49 +722,49 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2555.</t>
+          <t>5785.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19-Jun-2026 06:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3,44,40,000</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>34440000</v>
+        <v>10000000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>926.</t>
+          <t>2594.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -794,35 +794,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>3,44,40,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>31984321</v>
+        <v>34440000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>933.</t>
+          <t>937.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31803649</v>
+        <v>31984321</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,45 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3055.</t>
+          <t>940.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30-May-2026 01:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19-Jun-2026 03:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2,70,53,943</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>27053943</v>
+        <v>31803649</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,43 +958,101 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1091.</t>
+          <t>3078.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>30-May-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>19-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2,70,53,943</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>27053943</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Punjab eProcurement</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1108.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>1,67,51,919</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>16751919</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>244.</t>
+          <t>265.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>636.</t>
+          <t>702.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2100.</t>
+          <t>2296.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>714.</t>
+          <t>882.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5785.</t>
+          <t>5986.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2594.</t>
+          <t>1268.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -794,35 +794,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19-Jun-2026 06:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3,44,40,000</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>34440000</v>
+        <v>31984321</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>937.</t>
+          <t>1108.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31984321</v>
+        <v>31803649</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,159 +900,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>940.</t>
+          <t>1248.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>1,67,51,919</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>31803649</v>
+        <v>16751919</v>
       </c>
       <c r="L9" t="inlineStr">
-        <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JK eTenders</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>32</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3078.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>30-May-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20-Jun-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2,70,53,943</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>27053943</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Punjab eProcurement</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>32</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1108.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1,67,51,919</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>16751919</v>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>702.</t>
+          <t>703.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2296.</t>
+          <t>2277.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>882.</t>
+          <t>886.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5986.</t>
+          <t>6018.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1268.</t>
+          <t>1273.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1108.</t>
+          <t>1110.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1248.</t>
+          <t>1252.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>265.</t>
+          <t>312.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>703.</t>
+          <t>806.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2277.</t>
+          <t>2315.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>886.</t>
+          <t>942.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6018.</t>
+          <t>6162.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1273.</t>
+          <t>1401.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1110.</t>
+          <t>1228.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1252.</t>
+          <t>1293.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>312.</t>
+          <t>45.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>15-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>16-Jul-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>9,55,97,065</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>29140100</v>
+        <v>95597065</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -552,45 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>806.</t>
+          <t>8.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-Jun-2026 11:00 AM</t>
+          <t>22-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>06-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23-Jun-2026 11:00 AM</t>
+          <t>06-Jul-2026 03:30 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
+          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HP SIDC Limited</t>
+          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2,79,52,391</t>
+          <t>4,50,46,000</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>27952391</v>
+        <v>45046000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2315.</t>
+          <t>333.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>12-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>30-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>2,91,40,100</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>15861542</v>
+        <v>29140100</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>942.</t>
+          <t>2160.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11000000</v>
+        <v>15861542</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -726,45 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6162.</t>
+          <t>1004.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,53 +776,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1401.</t>
+          <t>5975.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>31984321</v>
+        <v>10000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1228.</t>
+          <t>1516.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31803649</v>
+        <v>31984321</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,43 +900,101 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1293.</t>
+          <t>1285.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>12-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,18,03,649</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>31803649</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Punjab eProcurement</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>32</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1230.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>1,67,51,919</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>16751919</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.</t>
+          <t>167.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>24.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>333.</t>
+          <t>348.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2160.</t>
+          <t>2151.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1004.</t>
+          <t>1037.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5975.</t>
+          <t>5612.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1516.</t>
+          <t>1574.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1285.</t>
+          <t>1367.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1230.</t>
+          <t>1256.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>167.</t>
+          <t>134.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>22-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15-Jul-2026 05:00 PM</t>
+          <t>06-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16-Jul-2026 09:00 AM</t>
+          <t>06-Jul-2026 03:30 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
+          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
+          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9,55,97,065</t>
+          <t>4,50,46,000</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>95597065</v>
+        <v>45046000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -552,45 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>420.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22-Jun-2026 04:15 PM</t>
+          <t>12-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:00 PM</t>
+          <t>30-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:30 PM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
+          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
+          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4,50,46,000</t>
+          <t>2,91,40,100</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>45046000</v>
+        <v>29140100</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>348.</t>
+          <t>328.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>25-Jun-2026 03:15 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>14-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>15-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction of Demonstration Rooms (06 nos.) on roof top of third Floor of Main College Building of GMC Kathua (Under Capex Budget 2025-26).] [e-NIT No.PWD/SE/KS/20 of 2026-27 Dated 24-06-2026][2026_PWDJK_313615_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>2,81,43,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>29140100</v>
+        <v>28143000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ShxFWwxuYULc%2Bn9QBbDXZDA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2151.</t>
+          <t>82.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>03-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Const of covered auction platfarm 230ftx80ft by Self Supporting Metallic roofing front side of office building at Kums Pratapgarh] [RSAMB/BHILWARA/NIB NO 06/2026-27 ][2026_RSAMB_571264_12]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Ajmer||Ex.En. - Chittorgarh</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>1,59,20,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15861542</v>
+        <v>15920000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST2YIs%2B7rDVdRUX8DbBYeDA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1037.</t>
+          <t>1325.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5612.</t>
+          <t>4863.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>03-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1574.</t>
+          <t>193.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>17-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>18-Jul-2026 12:00 PM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>PWD||CE RandB Jammu</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>8,46,91,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31984321</v>
+        <v>84691000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,45 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1367.</t>
+          <t>377.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>23-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>04-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>6,07,83,682</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>31803649</v>
+        <v>60783682</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,45 +958,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1256.</t>
+          <t>683.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24-Jun-2026 05:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
+          <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1,67,51,919</t>
+          <t>1,39,27,000</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>16751919</v>
+        <v>13927000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
         </is>
       </c>
     </row>

--- a/review_tenders.xlsx
+++ b/review_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,53 +486,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>134.</t>
+          <t>1283.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22-Jun-2026 04:15 PM</t>
+          <t>19-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:00 PM</t>
+          <t>18-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:30 PM</t>
+          <t>20-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
+          <t>[Major Civil Repairs Work at Administrative Block Building, AJNIFM Campus, Sector-48, Faridabad (Haryana)] [AJNIFM/Civil/2026-27/02][2026_DEXP_913889_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
+          <t>Department of Expenditure||National Institute of Financial Management,DoE,MoF||Administration-NIFM - DOE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4,50,46,000</t>
+          <t>1,60,53,363</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>45046000</v>
+        <v>16053363</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqLIcR0oNNfX%2FttiKnGHdeQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -552,45 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>420.</t>
+          <t>836.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>20-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>13-Jul-2026 11:30 AM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>13-Jul-2026 12:30 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction of Govt ITI Building G plus 5 Centre of Excellence at Nangal Distt Ropar ] [Tender Notice No. 9 Dated 19.06.2026][2026_CEPW_170505_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>CE-PWD(B and R)||Construction Circle-Chandigarh||Construction Division-Ropar</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>19,43,71,801</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>29140100</v>
+        <v>194371801</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6W2ferMHIsjtTQZh3GJ0wQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>328.</t>
+          <t>3898.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25-Jun-2026 03:15 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14-Jul-2026 04:00 PM</t>
+          <t>06-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15-Jul-2026 02:00 PM</t>
+          <t>09-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of Demonstration Rooms (06 nos.) on roof top of third Floor of Main College Building of GMC Kathua (Under Capex Budget 2025-26).] [e-NIT No.PWD/SE/KS/20 of 2026-27 Dated 24-06-2026][2026_PWDJK_313615_1]</t>
+          <t>[Construction work for the Fire Station and Garage Wing of the Bundi Municipal Council.] [NPB/Nirman/2026-27/3144 Dated 05/06/2026][2026_DLB_567746_3]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
+          <t>DLB||Dy.DR-Kota||Commissioner-Bundi</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2,81,43,000</t>
+          <t>10,93,04,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>28143000</v>
+        <v>109304000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ShxFWwxuYULc%2Bn9QBbDXZDA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SOcbSjzEC3BXIQm3Q51hqtQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>82.</t>
+          <t>4187.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>20-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>03-Jul-2026 06:00 PM</t>
+          <t>13-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>06-Jul-2026 11:00 AM</t>
+          <t>14-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Const of covered auction platfarm 230ftx80ft by Self Supporting Metallic roofing front side of office building at Kums Pratapgarh] [RSAMB/BHILWARA/NIB NO 06/2026-27 ][2026_RSAMB_571264_12]</t>
+          <t>[Neurovascular Intervention Implant for Neurosurgery Department] [1377_19.05.2026][2026_SMSMC_560591_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RSAMB||ACE - Zone I||S.E. - Circle Ajmer||Ex.En. - Chittorgarh</t>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,59,20,000</t>
+          <t>10,00,00,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15920000</v>
+        <v>100000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST2YIs%2B7rDVdRUX8DbBYeDA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SCH1R%2FLkR%2BnUKTAurOmciqg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,53 +718,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1325.</t>
+          <t>3892.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>15-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>07-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>10-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of Govt. ITI Building (4 Trade) at Bardod, Distt. Kotputli-Behror] [RSAMB/Alwar/NIT-07/2026-27(1)][2026_RSAMB_567646_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Jaipur||Ex.En. - Alwar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>7,43,29,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11000000</v>
+        <v>74329000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMcp3WJpJVJkSxOx6W8N2gw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4863.</t>
+          <t>25.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>02-Jul-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01-Jul-2026 02:00 PM</t>
+          <t>14-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>03-Jul-2026 04:00 PM</t>
+          <t>15-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[MRI, CT Scan and X-ray films for Radiodiagnosis dept.] [06/2026-27][2026_GMCK_572227_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Govt. Medical College, Kota||Principal and Controller</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>5,68,00,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>10000000</v>
+        <v>56800000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S5lOBWFRPRjKrz8WUhp%2B1Mw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,53 +834,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>193.</t>
+          <t>1072.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:00 PM</t>
+          <t>29-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17-Jul-2026 04:00 PM</t>
+          <t>08-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18-Jul-2026 12:00 PM</t>
+          <t>09-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
+          <t>[Mechanized Cleaning and Senitation Services] [mechanized cleaning and sanitation service ][2026_SNMCJ_571544_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PWD||CE RandB Jammu</t>
+          <t>Dr. S.N.Medical College, Jodhpur||Principal-and-Controller||Superintendent- Umed Hospital</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8,46,91,000</t>
+          <t>5,25,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>84691000</v>
+        <v>52500000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S18rI9ojqNkY1Cda93%2BNNpA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,53 +892,53 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>377.</t>
+          <t>3051.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23-Jun-2026 05:00 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>03-Jul-2026 04:00 PM</t>
+          <t>16-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>04-Jul-2026 11:00 AM</t>
+          <t>16-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
+          <t>[Security Guard Skilled worker Tender for RNT Medical College and Attached Hospitals for One Year] [1387][2026_RNTMC_570234_2]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>RNT Medical College, Udaipur||Principal and Controller.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6,07,83,682</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>60783682</v>
+        <v>50000000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2BvYNLR0%2BmxX%2FgWsG0t4ZyA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -954,47 +954,1149 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1949.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>31-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Miscellaneous Items for HPB and Liver Transplant Surgery OT] [1711_24.06.2026][2026_SMSMC_571079_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,25,00,000</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SgnhV0AOaF30etap8FNepJA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>946.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>31-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[neurosurgery items consumable, proprietory,implants tender] [436][2026_GMCK_571795_1]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller||Superintendent, Super Speciality Hospital Kota</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3,45,00,000</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SVY8L16B%2B9sz39EznSAOBBA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>293.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[Construction of administratve block of Police Station Aakola at Distt. Chittorgarh] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_2]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,16,40,000</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>31640000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMXLsU4fDnpy8pNfYftL3Kw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4156.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>29-May-2026 05:30 PM</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[Construction Work of Library and Co-Working Station Building in Sawai Madhopur] [E-NIT No. 04/2026-27 UIT Sawai Madhopur ][2026_UITSM_563395_1]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>UIT - SAWAI MADHOPUR||SECRETARY||EXECUTIVE ENGINEER</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,00,00,000</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sh38dQxKdtdyvKhLKMX7nAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2902.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[BALANCE WORK FOR CONSTRUCTION OF NEW PAVILLION BUILDING AND OTHER ALLIED WORKS AT SUBASH STADIUM UDHMAPUR 2nd time ] [e nit 12 of 2026-27 dated 20.06.2026][2026_SPORT_313266_1]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>J and K State Sports Council||Sports Council Construction Div Jammu</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2,92,74,000</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>29274000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S9jWeTiz91AXTipQZplL8vg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Uttarakhand eTenders</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>214.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[Construction work of restaurant and community centre under Vibrant Village in village Rongkong of development block Dharchula] [329 DATED 23-06-2026][2026_RES_96930_1]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RES - Chief Engineer||SE - Pithoragarh</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2,84,90,000</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>28490000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScuXPTCf2qgSeP5Ho2OAWPQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>964.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[KITCHEN AND DIETARY SERVICES] [MCGMC/E-TENDER/2026/0003][2026_HRY_531897_1]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Maharishi Chyawan Medical College Koriawas Narnaul</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2,50,00,000</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SrJ9LRlgIfIaDXDKDCQLj5Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1300.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 05:50 PM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[Library Books] [MCGMC/E-TENDER/2026/0001][2026_HRY_531408_1]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Maharishi Chyawan Medical College Koriawas Narnaul</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2,50,00,000</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SyW7Kri2R3OCjLewhnCvr4w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4199.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>15-May-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[Surgical And Suture Items Tender] [212][2026_GMCK_559661_1]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller||Superintendent, Super Speciality Hospital Kota</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2,12,00,000</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>21200000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScbrvXhGmoKQgtGAXfYxdKA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1388.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[Rough Cost Estimate for Various Construction works in Community Centre Sector-46 Ward No.20, Faridabad.] [202695CC0C9C FA7A 4968 BE73 7681F457F169284ULB][2026_HRY_531268_1]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Haryana Government||Urban Local Bodies||Faridabad</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1,93,54,683</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>19354683</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SloPzjrH0560YEBA7BHgYpA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2183.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[Dismantling and reconstruction of food store building at Hiranagar.] [e-NIT No.PWD/SE/KS/17 of 2026-27 Dated 22-06-2026][2026_PWDJK_313596_1]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1,71,91,000</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>17191000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SV0hDtoZc4nr5h8jv1EdsVw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>35</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1155.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[Service Contract] [PT/NRS/BH/14A][2026_HRY_531744_1]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Pt. Nekiram Sharma Govt. Medical College Bhiwani</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1,60,00,000</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si36wYGtipFe0hiuYvqSHPA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2256.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[Construction of New PHC Building at Burja (Block Malakhera) Distt. Alwar] [NIT NO. 07/2026-27(21)eemhalwar][2026_MEDIC_570999_1]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1,40,00,000</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SyQosoh%2FL1WEJUv%2FKgXTnAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>35</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>471.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>27-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[Construction of Sub-Tehsil Building at Majheen, Distt.Kangra(H.P)] [1514-15 dated 0206.2026][2026_PWD_137564_1]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PWD</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1,12,64,584</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>11264584</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SCGn9fBlgLprVNPXsoOHr6w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1050.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[Miscellaneous balance civil works of Plant and Non plant buildings at SSCTPS Suratgarh] [TN/STPS-SC/2026-27/290(Civil)][2026_RRVUN_570745_1]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RRVUN - CMD||RVUN-CE (STPS-SC) SURATGARH</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1,10,71,370</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>11071370</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SospqnumSIEQgOinMxutOlQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3068.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[4k ICG Laparoscopic Endovision System] [1382][2026_RNTMC_570127_1]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RNT Medical College, Udaipur||Principal and Controller.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1,00,00,000</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0kcBOnrt7Ree4DBm7tOGng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>32</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>683.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1994.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>17-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>18-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>8,46,91,000</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>84691000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>691.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6,07,83,682</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>60783682</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>32</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>34.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[Construction of residences for Judicial Officers in Judicial Court Complex at Sector 27, Pinjore in District- Panchkula] [2026AA86EF83 87EC 456A B50B E053BF193A04619BAR][2026_HRY_532891_1]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE NH Panchkula</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4,93,28,386</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>49328386</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SUWmDcRlY6pUHY55gbdhOMA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>32</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2248.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>25-Jun-2026 09:00 AM</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>1,39,27,000</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K29" t="n">
         <v>13927000</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
         </is>
